--- a/templates/E_PROM_FAHP_Express_Template.xlsx
+++ b/templates/E_PROM_FAHP_Express_Template.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,13 +36,27 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7E6E6"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -63,12 +77,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -143,6 +168,51 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>E-PROM</author>
+  </authors>
+  <commentList>
+    <comment ref="B4" authorId="0" shapeId="0">
+      <text>
+        <t>Critério de referência: deve ser o mais importante e é fixado em 1. Para mudar a referência, coloque o critério desejado como primeiro critério na planilha de avaliações.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>E-PROM</author>
+  </authors>
+  <commentList>
+    <comment ref="B4" authorId="0" shapeId="0">
+      <text>
+        <t>Critério de referência: deve ser o mais importante e é fixado em 1. Para mudar a referência, coloque o critério desejado como primeiro critério na planilha de avaliações.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>E-PROM</author>
+  </authors>
+  <commentList>
+    <comment ref="B4" authorId="0" shapeId="0">
+      <text>
+        <t>Critério de referência: deve ser o mais importante e é fixado em 1. Para mudar a referência, coloque o critério desejado como primeiro critério na planilha de avaliações.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -434,97 +504,136 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Linha de referência FAHP-Express</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr"/>
-      <c r="C1" s="2" t="inlineStr"/>
-      <c r="D1" s="2" t="inlineStr"/>
-      <c r="E1" s="2" t="inlineStr"/>
-      <c r="F1" s="2" t="inlineStr"/>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>FAHP-Express — Referência e Precisão</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="n"/>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Critérios</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Impacto da Missão</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Custo (R$)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Desempenho</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Prazo (meses)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Risco Técnico</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Referência</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Comparação com referência</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Precisão do atributo</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Não aplicável</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Não aplicável</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Não aplicável</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n"/>
+    </row>
+    <row r="8"/>
   </sheetData>
   <autoFilter ref="A1:F4"/>
+  <dataValidations count="2">
+    <dataValidation sqref="C4:F4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Valor inválido" error="Informe um valor entre 1 e 9." promptTitle="FAHP-Express" prompt="Fator relativo à importância do critério de referência." type="decimal" operator="between">
+      <formula1>1</formula1>
+      <formula2>9</formula2>
+    </dataValidation>
+    <dataValidation sqref="B5:F5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Alta,Média,Baixa,Não aplicável"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -534,97 +643,136 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Linha de referência FAHP-Express</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr"/>
-      <c r="C1" s="2" t="inlineStr"/>
-      <c r="D1" s="2" t="inlineStr"/>
-      <c r="E1" s="2" t="inlineStr"/>
-      <c r="F1" s="2" t="inlineStr"/>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>FAHP-Express — Referência e Precisão</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="n"/>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Critérios</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Impacto da Missão</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Custo (R$)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Desempenho</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Prazo (meses)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Risco Técnico</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Referência</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Comparação com referência</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Precisão do atributo</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Não aplicável</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Não aplicável</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Não aplicável</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n"/>
+    </row>
+    <row r="8"/>
   </sheetData>
   <autoFilter ref="A1:F4"/>
+  <dataValidations count="2">
+    <dataValidation sqref="C4:F4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Valor inválido" error="Informe um valor entre 1 e 9." promptTitle="FAHP-Express" prompt="Fator relativo à importância do critério de referência." type="decimal" operator="between">
+      <formula1>1</formula1>
+      <formula2>9</formula2>
+    </dataValidation>
+    <dataValidation sqref="B5:F5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Alta,Média,Baixa,Não aplicável"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -634,97 +782,136 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Linha de referência FAHP-Express</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr"/>
-      <c r="C1" s="2" t="inlineStr"/>
-      <c r="D1" s="2" t="inlineStr"/>
-      <c r="E1" s="2" t="inlineStr"/>
-      <c r="F1" s="2" t="inlineStr"/>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>FAHP-Express — Referência e Precisão</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="n"/>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Critérios</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Impacto da Missão</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Custo (R$)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Desempenho</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Prazo (meses)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Risco Técnico</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Referência</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Comparação com referência</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Precisão do atributo</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Não aplicável</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Não aplicável</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Não aplicável</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n"/>
+    </row>
+    <row r="8"/>
   </sheetData>
   <autoFilter ref="A1:F4"/>
+  <dataValidations count="2">
+    <dataValidation sqref="C4:F4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Valor inválido" error="Informe um valor entre 1 e 9." promptTitle="FAHP-Express" prompt="Fator relativo à importância do critério de referência." type="decimal" operator="between">
+      <formula1>1</formula1>
+      <formula2>9</formula2>
+    </dataValidation>
+    <dataValidation sqref="B5:F5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Alta,Média,Baixa,Não aplicável"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -734,11 +921,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -761,33 +948,105 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Informe a referência linguística/numerical do FAHP-Express para cada critério.</t>
+          <t>Linha de comparação com o critério de referência.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Critérios</t>
+          <t>Primeiro critério</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A ordem deve ser idêntica à planilha de avaliações.</t>
+          <t>É sempre a referência e deve ser o mais importante. Sua própria comparação é fixada em 1.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Escala</t>
+          <t>Demais critérios</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Use a escala Saaty 1–9 ou as expressões linguísticas disponíveis no E-PROM.</t>
-        </is>
-      </c>
+          <t>3 = a referência é três vezes mais importante que o critério correspondente. Use fatores de 1 a 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Precisão do atributo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Para critérios contínuos, escolha Alta, Média ou Baixa. Para critérios ordinais, use Não aplicável.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Trapezoide fuzzy estreito: suporte ±5% e núcleo ±2% (parâmetros internos do método).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Trapezoide fuzzy intermediário: suporte ±10% e núcleo ±4% (parâmetros internos do método).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Trapezoide fuzzy amplo: suporte ±16,6667% e núcleo ±6,6667% (parâmetros internos do método).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Exemplo</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Para x=300000 e precisão Baixa: aproximadamente [250000, 280000, 320000, 350000].</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:B4"/>

--- a/templates/E_PROM_FAHP_Express_Template.xlsx
+++ b/templates/E_PROM_FAHP_Express_Template.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,6 @@
       <c r="E1" s="4" t="n"/>
       <c r="F1" s="4" t="n"/>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -590,7 +589,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Não aplicável</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -600,7 +599,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Não aplicável</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -610,7 +609,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Não aplicável</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
@@ -620,7 +619,6 @@
     <row r="7">
       <c r="A7" s="2" t="n"/>
     </row>
-    <row r="8"/>
   </sheetData>
   <autoFilter ref="A1:F4"/>
   <dataValidations count="2">
@@ -643,7 +641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -666,7 +664,6 @@
       <c r="E1" s="4" t="n"/>
       <c r="F1" s="4" t="n"/>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -729,7 +726,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Não aplicável</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -739,7 +736,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Não aplicável</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -749,7 +746,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Não aplicável</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
@@ -759,7 +756,6 @@
     <row r="7">
       <c r="A7" s="2" t="n"/>
     </row>
-    <row r="8"/>
   </sheetData>
   <autoFilter ref="A1:F4"/>
   <dataValidations count="2">
@@ -782,7 +778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -805,7 +801,6 @@
       <c r="E1" s="4" t="n"/>
       <c r="F1" s="4" t="n"/>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -868,7 +863,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Não aplicável</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -878,7 +873,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Não aplicável</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -888,7 +883,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Não aplicável</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
@@ -898,7 +893,6 @@
     <row r="7">
       <c r="A7" s="2" t="n"/>
     </row>
-    <row r="8"/>
   </sheetData>
   <autoFilter ref="A1:F4"/>
   <dataValidations count="2">
@@ -984,7 +978,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Para critérios contínuos, escolha Alta, Média ou Baixa. Para critérios ordinais, use Não aplicável.</t>
+          <t>É sempre a referência e deve ser o mais importante. Sua própria comparação é fixada em 1.</t>
         </is>
       </c>
     </row>
@@ -996,7 +990,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Trapezoide fuzzy estreito: suporte ±5% e núcleo ±2% (parâmetros internos do método).</t>
+          <t>3 = a referência é três vezes mais importante que o critério correspondente. Use fatores de 1 a 9.</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1002,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Trapezoide fuzzy intermediário: suporte ±10% e núcleo ±4% (parâmetros internos do método).</t>
+          <t>Para qualquer critério, escolha Alta, Média ou Baixa. A precisão controla a largura do trapezoide fuzzy.</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1014,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Trapezoide fuzzy amplo: suporte ±16,6667% e núcleo ±6,6667% (parâmetros internos do método).</t>
+          <t>Alta: menor incerteza fuzzy. Média: representação fuzzy padrão. Baixa: maior incerteza fuzzy.</t>
         </is>
       </c>
     </row>
@@ -1032,13 +1026,17 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Para x=300000 e precisão Baixa: aproximadamente [250000, 280000, 320000, 350000].</t>
+          <t>Ordinal: a representação padrão é contraída/dilatada em torno do valor observado e limitada à escala.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
-      <c r="B10" s="3" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Contínuo: o trapezoide é construído na unidade original do atributo, usando os parâmetros internos de precisão.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>

--- a/templates/E_PROM_FAHP_Express_Template.xlsx
+++ b/templates/E_PROM_FAHP_Express_Template.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -599,15 +599,20 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
@@ -641,7 +646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -726,25 +731,30 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
@@ -778,7 +788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -868,22 +878,27 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Média</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
         </is>
       </c>
     </row>
